--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="battle_log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="overall_stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-19 08:00:00</t>
+          <t>2026-04-19 10:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,33 +532,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>RED_3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
       <c r="K2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -570,19 +571,19 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ничья</t>
+          <t>победа</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-19 08:15:00</t>
+          <t>2026-04-19 10:15:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,63 +593,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BLU_3</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
+        <v>58</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>RED_3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>засада</t>
+          <t>разгром</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-19 08:30:00</t>
+          <t>2026-04-19 10:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -658,7 +659,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -667,20 +668,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -689,7 +690,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -714,7 +715,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-19 08:45:00</t>
+          <t>2026-04-19 10:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -724,63 +725,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>27</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>RED_4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>победа</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-19 09:00:00</t>
+          <t>2026-04-19 10:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -795,46 +796,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>27</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>RED_4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -846,7 +847,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-19 09:15:00</t>
+          <t>2026-04-19 10:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -856,51 +857,51 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLU_6</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>RED_4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -912,7 +913,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-19 09:30:00</t>
+          <t>2026-04-19 10:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -922,63 +923,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLU_1</t>
+          <t>BLU_4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>84</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>RED_6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>победа</t>
+          <t>ничья</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-19 09:45:00</t>
+          <t>2026-04-19 11:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -988,7 +989,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLU_3</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -997,20 +998,20 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1019,13 +1020,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1037,14 +1038,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>разгром</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-19 10:00:00</t>
+          <t>2026-04-19 11:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1054,452 +1055,56 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLU_2</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>82</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>60</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>RED_5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>победа</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04-19 10:15:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BLU_5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>27</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>RED_3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>поражение</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-04-19 10:30:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BLU_1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>58</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>RED_5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>победа</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-04-19 10:45:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>43</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>60</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>ничья</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:00:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BLU_4</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>30</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>RED_6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>30</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>разгром</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:15:00</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BLU_5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>60</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>поражение</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:30:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>43</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>60</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>поражение</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,40 +1160,50 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>blue_arm_before</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>blue_cas_inf</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>blue_cas_armor</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>red_force_before</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>red_arm_before</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>red_cas_inf</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>red_cas_armor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>distance</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>blue_cover</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>red_cover</t>
         </is>
@@ -1600,7 +1215,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-19 08:00:00</t>
+          <t>2026-04-19 10:00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1610,44 +1225,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RED_3</t>
+          <t>RED_2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ничья</t>
+          <t>победа</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1657,12 +1278,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-19 08:15:00</t>
+          <t>2026-04-19 10:15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BLU_3</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1672,40 +1293,46 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>засада</t>
+          <t>разгром</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>58</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>17</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>60</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1714,17 +1341,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-19 08:30:00</t>
+          <t>2026-04-19 10:00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1738,30 +1365,36 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1771,55 +1404,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-19 08:45:00</t>
+          <t>2026-04-19 10:30:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>победа</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1828,7 +1467,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-19 09:00:00</t>
+          <t>2026-04-19 10:30:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1838,12 +1477,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1852,31 +1491,37 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1885,22 +1530,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-19 09:15:00</t>
+          <t>2026-04-19 10:45:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLU_6</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1909,30 +1554,36 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1942,55 +1593,61 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-19 09:30:00</t>
+          <t>2026-04-19 10:45:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLU_1</t>
+          <t>BLU_4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RED_6</t>
+          <t>RED_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>победа</t>
+          <t>ничья</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1999,17 +1656,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-19 09:45:00</t>
+          <t>2026-04-19 11:00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLU_3</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2019,34 +1676,40 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>разгром</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2056,22 +1719,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-19 10:00:00</t>
+          <t>2026-04-19 11:00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLU_2</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RED_5</t>
+          <t>RED_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>mech_attacks_inf</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2080,372 +1743,36 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-19 10:15:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BLU_5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RED_3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>поражение</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>27</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>59</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-19 10:30:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BLU_1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RED_5</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>победа</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>58</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-19 10:45:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ничья</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>43</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>60</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:00:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BLU_4</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>RED_6</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>разгром</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>30</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:15:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BLU_5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>поражение</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>60</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:30:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>поражение</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>43</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>60</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2460,324 +1787,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>temp_unit_id</t>
+          <t>total_battles</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>slice_label</t>
+          <t>blue_victories</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>source_level</t>
+          <t>blue_defeats</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>source_uid</t>
+          <t>draws_or_other</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>split_basis</t>
+          <t>blue_cas_inf_total</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>soldiers</t>
+          <t>blue_cas_armor_total</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>company_uids</t>
+          <t>red_cas_inf_total</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>platoon_uids</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>squad_uids</t>
+          <t>red_cas_armor_total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BLU_1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>B1-C1-PART1[P1..P2]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>battalion</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
+      <c r="A2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>B1-C1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>B1-C1-P1,B1-C1-P2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BLU_2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>B1-C2-PART1[P1..P2]</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>battalion</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>B1-C2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>B1-C2-P1,B1-C2-P2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>B1-C3-PART1[P1..P2]</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>battalion</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>B1-C3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>B1-C3-P1,B1-C3-P2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BLU_4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>B1-C1-PART2[P3..P3]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>battalion</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>B1-C1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>B1-C1-P3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BLU_5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>B1-C2-PART2[P3..P3]</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>battalion</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>B1-C2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>B1-C2-P3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BLU_6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>B1-C3-PART2[P3..P3]</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>battalion</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>B1-C3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>B1-C3-P3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2791,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,19 +1880,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>source_level</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_uid</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>slice_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>source_level</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source_uid</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>split_basis</t>
@@ -2838,276 +1916,584 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>squad_uids</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role_armor</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>assigned_armor</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>source_armor_uids</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RED_1</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B1-C1-PART1[P1..P2]</t>
+          <t>battalion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>battalion</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2-PART2[B2-C5..B2-C5]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>platoon</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B1-C1</t>
+          <t>B2-C5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>B1-C1-P1,B1-C1-P2</t>
+          <t>B2-C5-P1,B2-C5-P2,B2-C5-P3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
-        </is>
-      </c>
+          <t>B2-C5-P1-S1,B2-C5-P1-S2,B2-C5-P1-S3,B2-C5-P2-S1,B2-C5-P2-S2,B2-C5-P2-S3,B2-C5-P3-S1,B2-C5-P3-S2,B2-C5-P3-S3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RED_2</t>
+          <t>BLU_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B1-C2-PART1[P1..P2]</t>
+          <t>battalion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>battalion</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2-PART2[B2-C4..B2-C4]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>platoon</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B1-C2</t>
+          <t>B2-C4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>B1-C2-P1,B1-C2-P2</t>
+          <t>B2-C4-P1,B2-C4-P2,B2-C4-P3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+          <t>B2-C4-P1-S1,B2-C4-P1-S2,B2-C4-P1-S3,B2-C4-P2-S1,B2-C4-P2-S2,B2-C4-P2-S3,B2-C4-P3-S1,B2-C4-P3-S2,B2-C4-P3-S3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>A31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RED_3</t>
+          <t>BLU_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B1-C3-PART1[P1..P2]</t>
+          <t>battalion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>battalion</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2-PART2[B2-C3..B2-C3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>platoon</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B1-C3</t>
+          <t>B2-C3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B1-C3-P1,B1-C3-P2</t>
+          <t>B2-C3-P1,B2-C3-P2,B2-C3-P3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
-        </is>
-      </c>
+          <t>B2-C3-P1-S1,B2-C3-P1-S2,B2-C3-P1-S3,B2-C3-P2-S1,B2-C3-P2-S2,B2-C3-P2-S3,B2-C3-P3-S1,B2-C3-P3-S2,B2-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>BLU_4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B1-C1-PART2[P3..P3]</t>
+          <t>battalion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>battalion</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2-PART1[B2-C2..B2-C2]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>platoon</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B1-C1</t>
+          <t>B2-C2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>B1-C1-P3</t>
+          <t>B2-C2-P1,B2-C2-P2,B2-C2-P3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+          <t>B2-C2-P1-S1,B2-C2-P1-S2,B2-C2-P1-S3,B2-C2-P2-S1,B2-C2-P2-S2,B2-C2-P2-S3,B2-C2-P3-S1,B2-C2-P3-S2,B2-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>A29,A3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RED_5</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B1-C2-PART2[P3..P3]</t>
+          <t>battalion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>battalion</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2-PART1[B2-C1..B2-C1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>platoon</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B1-C2</t>
+          <t>B2-C1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>B1-C2-P3</t>
+          <t>B2-C1-P1,B2-C1-P2,B2-C1-P3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+          <t>B2-C1-P1-S1,B2-C1-P1-S2,B2-C1-P1-S3,B2-C1-P2-S1,B2-C1-P2-S2,B2-C1-P2-S3,B2-C1-P3-S1,B2-C1-P3-S2,B2-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RED_6</t>
+          <t>BLU_6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B1-C3-PART2[P3..P3]</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A2,A20,A25,A26,A27,A28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>temp_unit_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source_level</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_uid</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slice_label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>split_basis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>soldiers</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>company_uids</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>platoon_uids</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>squad_uids</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>battalion</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>platoon</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>B1-C3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>B1-C3-P3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B2-PART2[B2-C3..B2-C3]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>89</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B2-C3-P1,B2-C3-P2,B2-C3-P3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>B2-C3-P1-S1,B2-C3-P1-S2,B2-C3-P1-S3,B2-C3-P2-S1,B2-C3-P2-S2,B2-C3-P2-S3,B2-C3-P3-S1,B2-C3-P3-S2,B2-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>battalion</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B2-PART2[B2-C2..B2-C2]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B2-C2-P1,B2-C2-P2,B2-C2-P3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>B2-C2-P1-S1,B2-C2-P1-S2,B2-C2-P1-S3,B2-C2-P2-S1,B2-C2-P2-S2,B2-C2-P2-S3,B2-C2-P3-S1,B2-C2-P3-S2,B2-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>battalion</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B2-PART1[B2-C1..B2-C1]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>B2-C1-P1,B2-C1-P2,B2-C1-P3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>B2-C1-P1-S1,B2-C1-P1-S2,B2-C1-P1-S3,B2-C1-P2-S1,B2-C1-P2-S2,B2-C1-P2-S3,B2-C1-P3-S1,B2-C1-P3-S2,B2-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
         </is>
       </c>
     </row>

--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,6 +601,43 @@
       </c>
       <c r="K4" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46118.25</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B2 штурмует Рубежкевичи</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -614,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2175,6 +2212,609 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:00:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>42</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>mech_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:15:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>38</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>84</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>mech_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:00:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>84</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>36</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>84</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>inf_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:15:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>48</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>inf_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:30:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>48</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>84</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>inf_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>84</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>42</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>mech_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:45:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>84</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>inf_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-06 06:30:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>27</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>40</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:00:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>84</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>84</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>18</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>mech_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>ничья</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3357,6 +3997,432 @@
         <v>12</v>
       </c>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>A1,A10,A11,A12,A13,A14,A15,A16,A17,A18,A19,A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>84</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>A21,A23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>84</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>84</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>A24,A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>42</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>42</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>42</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BLU_7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BLU_7</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>12</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>A1,A10,A11,A12,A13,A14,A15,A16,A17,A18,A19,A2</t>
         </is>
@@ -3373,7 +4439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3432,6 +4498,21 @@
           <t>unit_role</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role_armor</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>assigned_armor</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>source_armor_uids</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3485,6 +4566,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3538,6 +4622,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3591,6 +4678,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3644,6 +4734,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3697,6 +4790,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3750,6 +4846,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3803,6 +4902,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3856,6 +4958,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3909,6 +5014,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3962,6 +5070,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4015,6 +5126,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4068,6 +5182,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4121,6 +5238,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4174,6 +5294,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4227,6 +5350,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4280,6 +5406,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4333,6 +5462,9 @@
           <t>inf_or_mech</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4384,6 +5516,451 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>84</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>84</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>84</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>42</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>42</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>42</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RED_7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RED_7</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>12</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>A1,A10,A11,A12,A13,A14,A15,A16,A17,A18,A19,A2</t>
         </is>
       </c>
     </row>

--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="tactical_log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ground_log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="player_plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="enemy_plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tactical_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ground_log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,117 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>124</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>56</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>43</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1145,7 +1256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9493,6 +9604,2619 @@
       <c r="Q124" t="inlineStr">
         <is>
           <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>36</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>18</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>72</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>36</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>7</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>36</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>72</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>15</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>72</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>29</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>23</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>36</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>36</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>36</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>72</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>18</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>13</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>72</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>72</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>36</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>70</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>36</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>69</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>36</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>11</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>57</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>72</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>6</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>72</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>3</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>71</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>72</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>36</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>72</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>72</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>36</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>36</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>36</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>71</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>72</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>33</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>69</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>36</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>36</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>70</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>22</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>72</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>29</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>16</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>72</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>72</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>5</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>36</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>11</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>13</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>13</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>25</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:15:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>67</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>4</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>25</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>69</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>70</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>36</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>36</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>72</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>72</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>3</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>72</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>36</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>71</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>36</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>72</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>72</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>10</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>36</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>36</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>34</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>62</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>71</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>36</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>36</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>36</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>34</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>72</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>32</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>5</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>36</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>71</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>36</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>70</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>9</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>69</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>70</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>8</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>36</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>36</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>10</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>67</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>засада</t>
         </is>
       </c>
     </row>
@@ -9507,7 +12231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14650,6 +17374,960 @@
         </is>
       </c>
       <c r="K97" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>19</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B10-C3</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>B10-C3-PART1[B10-C3-P1..B10-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>72</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>B10-C3</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>B10-C3-P1,B10-C3-P3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>B10-C3-P1-S1,B10-C3-P1-S2,B10-C3-P1-S3,B10-C3-P3-S1,B10-C3-P3-S2,B10-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>19</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>B10-C2</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>B10-C2-PART1[B10-C2-P1..B10-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>72</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>B10-C2</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>B10-C2-P1,B10-C2-P3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>B10-C2-P1-S1,B10-C2-P1-S2,B10-C2-P1-S3,B10-C2-P3-S1,B10-C2-P3-S2,B10-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>19</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B10-C1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>B10-C1-PART1[B10-C1-P1..B10-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>72</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>B10-C1</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>B10-C1-P1,B10-C1-P3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>B10-C1-P1-S1,B10-C1-P1-S2,B10-C1-P1-S3,B10-C1-P3-S1,B10-C1-P3-S2,B10-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>19</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>B10-C3-P2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>B10-C3-PART2[B10-C3-P2..B10-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>36</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>B10-C3</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>B10-C3-P2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>B10-C3-P2-S1,B10-C3-P2-S2,B10-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>19</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>B10-C2-P2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B10-C2-PART2[B10-C2-P2..B10-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>36</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>B10-C2</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>B10-C2-P2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>B10-C2-P2-S1,B10-C2-P2-S2,B10-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>19</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>B10-C1-P2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>B10-C1-PART2[B10-C1-P2..B10-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>36</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>B10-C1</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>B10-C1-P2</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>B10-C1-P2-S1,B10-C1-P2-S2,B10-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>19</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>B10-C3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>B10-C3-PART1[B10-C3-P1..B10-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>72</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>B10-C3</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>B10-C3-P1,B10-C3-P3</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>B10-C3-P1-S1,B10-C3-P1-S2,B10-C3-P1-S3,B10-C3-P3-S1,B10-C3-P3-S2,B10-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>19</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>B10-C2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>B10-C2-PART1[B10-C2-P1..B10-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>72</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>B10-C2</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>B10-C2-P1,B10-C2-P3</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>B10-C2-P1-S1,B10-C2-P1-S2,B10-C2-P1-S3,B10-C2-P3-S1,B10-C2-P3-S2,B10-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>19</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>B10-C1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>B10-C1-PART1[B10-C1-P1..B10-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>72</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>B10-C1</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>B10-C1-P1,B10-C1-P3</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>B10-C1-P1-S1,B10-C1-P1-S2,B10-C1-P1-S3,B10-C1-P3-S1,B10-C1-P3-S2,B10-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>19</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>B10-C3-P2</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>B10-C3-PART2[B10-C3-P2..B10-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>36</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>B10-C3</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>B10-C3-P2</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>B10-C3-P2-S1,B10-C3-P2-S2,B10-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>19</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>B10-C2-P2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>B10-C2-PART2[B10-C2-P2..B10-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>36</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>B10-C2</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>B10-C2-P2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>B10-C2-P2-S1,B10-C2-P2-S2,B10-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>19</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>B10-C1-P2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>B10-C1-PART2[B10-C1-P2..B10-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>36</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>B10-C1</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>B10-C1-P2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>B10-C1-P2-S1,B10-C1-P2-S2,B10-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>19</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>72</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>19</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>72</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>19</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>72</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>19</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>36</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>19</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>36</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>19</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>36</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>inf_or_mech</t>
         </is>
@@ -14666,7 +18344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19814,6 +23492,960 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>19</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B5-C3</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>B5-C3-PART1[B5-C3-P1..B5-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>72</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>B5-C3</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>B5-C3-P1,B5-C3-P3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>B5-C3-P1-S1,B5-C3-P1-S2,B5-C3-P1-S3,B5-C3-P3-S1,B5-C3-P3-S2,B5-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>19</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>B5-C2</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>B5-C2-PART1[B5-C2-P1..B5-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>72</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>B5-C2</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>B5-C2-P1,B5-C2-P3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>B5-C2-P1-S1,B5-C2-P1-S2,B5-C2-P1-S3,B5-C2-P3-S1,B5-C2-P3-S2,B5-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>19</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B5-C1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>B5-C1-PART1[B5-C1-P1..B5-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>72</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>B5-C1</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>B5-C1-P1,B5-C1-P3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>B5-C1-P1-S1,B5-C1-P1-S2,B5-C1-P1-S3,B5-C1-P3-S1,B5-C1-P3-S2,B5-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>19</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>B5-C3-P2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>B5-C3-PART2[B5-C3-P2..B5-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>36</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>B5-C3</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>B5-C3-P2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>B5-C3-P2-S1,B5-C3-P2-S2,B5-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>19</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>B5-C2-P2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B5-C2-PART2[B5-C2-P2..B5-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>36</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>B5-C2</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>B5-C2-P2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>B5-C2-P2-S1,B5-C2-P2-S2,B5-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>19</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>B5-C1-P2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>B5-C1-PART2[B5-C1-P2..B5-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>36</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>B5-C1</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>B5-C1-P2</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>B5-C1-P2-S1,B5-C1-P2-S2,B5-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>19</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>B5-C3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>B5-C3-PART1[B5-C3-P1..B5-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>72</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>B5-C3</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>B5-C3-P1,B5-C3-P3</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>B5-C3-P1-S1,B5-C3-P1-S2,B5-C3-P1-S3,B5-C3-P3-S1,B5-C3-P3-S2,B5-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>19</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>B5-C2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>B5-C2-PART1[B5-C2-P1..B5-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>72</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>B5-C2</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>B5-C2-P1,B5-C2-P3</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>B5-C2-P1-S1,B5-C2-P1-S2,B5-C2-P1-S3,B5-C2-P3-S1,B5-C2-P3-S2,B5-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>19</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>B5-C1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>B5-C1-PART1[B5-C1-P1..B5-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>72</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>B5-C1</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>B5-C1-P1,B5-C1-P3</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>B5-C1-P1-S1,B5-C1-P1-S2,B5-C1-P1-S3,B5-C1-P3-S1,B5-C1-P3-S2,B5-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>19</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>B5-C3-P2</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>B5-C3-PART2[B5-C3-P2..B5-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>36</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>B5-C3</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>B5-C3-P2</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>B5-C3-P2-S1,B5-C3-P2-S2,B5-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>19</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>B5-C2-P2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>B5-C2-PART2[B5-C2-P2..B5-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>36</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>B5-C2</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>B5-C2-P2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>B5-C2-P2-S1,B5-C2-P2-S2,B5-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>19</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>B5-C1-P2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>B5-C1-PART2[B5-C1-P2..B5-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>36</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>B5-C1</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>B5-C1-P2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>B5-C1-P2-S1,B5-C1-P2-S2,B5-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>19</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>72</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>19</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>72</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>19</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>72</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>19</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>36</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>19</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>36</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>19</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>36</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,6 +1242,80 @@
         <v>16</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>73</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1256,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q163"/>
+  <dimension ref="A1:Q190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12217,6 +12291,1841 @@
       <c r="Q163" t="inlineStr">
         <is>
           <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>72</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>7</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>36</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>72</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>18</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>72</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>36</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>36</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>65</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>36</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>54</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>36</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>2</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>36</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>36</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>54</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>8</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>36</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>35</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>72</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>33</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>16</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>72</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>64</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>7</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>72</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>36</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>72</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>36</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>34</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:15:00</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>34</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>4</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>69</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>57</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>36</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>3</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>19</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>72</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>36</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>19</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>36</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>36</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>19</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>32</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>3</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>72</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>19</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>72</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>3</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>36</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>19</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>72</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>10</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>72</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>19</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>36</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>6</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>36</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>19</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>62</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>4</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>35</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>19</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>58</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>11</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>35</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>19</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>36</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>35</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>6</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>19</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>47</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>3</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>71</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>2</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>19</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>29</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>35</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>19</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>30</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>3</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>72</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>19</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>27</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>29</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>поражение</t>
         </is>
       </c>
     </row>
@@ -12231,7 +14140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18328,6 +20237,642 @@
         </is>
       </c>
       <c r="K115" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>19</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>B2-C3-PART1[B2-C3-P1..B2-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>72</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>B2-C3-P1,B2-C3-P3</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>B2-C3-P1-S1,B2-C3-P1-S2,B2-C3-P1-S3,B2-C3-P3-S1,B2-C3-P3-S2,B2-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>19</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>B2-C2-PART1[B2-C2-P1..B2-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>72</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>B2-C2-P1,B2-C2-P3</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>B2-C2-P1-S1,B2-C2-P1-S2,B2-C2-P1-S3,B2-C2-P3-S1,B2-C2-P3-S2,B2-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>19</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>B2-C1-PART1[B2-C1-P1..B2-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>72</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>B2-C1-P1,B2-C1-P3</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>B2-C1-P1-S1,B2-C1-P1-S2,B2-C1-P1-S3,B2-C1-P3-S1,B2-C1-P3-S2,B2-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>19</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>B2-C3-P2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>B2-C3-PART2[B2-C3-P2..B2-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>36</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>B2-C3-P2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>B2-C3-P2-S1,B2-C3-P2-S2,B2-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>19</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>B2-C2-P2</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>B2-C2-PART2[B2-C2-P2..B2-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>36</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>B2-C2-P2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>B2-C2-P2-S1,B2-C2-P2-S2,B2-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>19</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>B2-C1-P2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>B2-C1-PART2[B2-C1-P2..B2-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>36</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>B2-C1-P2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>B2-C1-P2-S1,B2-C1-P2-S2,B2-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>19</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>B3-C3-PART1[B3-C3-P1..B3-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>72</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>B3-C3-P1,B3-C3-P3</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>B3-C3-P1-S1,B3-C3-P1-S2,B3-C3-P1-S3,B3-C3-P3-S1,B3-C3-P3-S2,B3-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>19</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>B3-C2-PART1[B3-C2-P1..B3-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>72</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>B3-C2-P1,B3-C2-P3</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>B3-C2-P1-S1,B3-C2-P1-S2,B3-C2-P1-S3,B3-C2-P3-S1,B3-C2-P3-S2,B3-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>19</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>B3-C1-PART1[B3-C1-P1..B3-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>72</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>B3-C1-P1,B3-C1-P3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>B3-C1-P1-S1,B3-C1-P1-S2,B3-C1-P1-S3,B3-C1-P3-S1,B3-C1-P3-S2,B3-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>19</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>B3-C3-P2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>B3-C3-PART2[B3-C3-P2..B3-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>36</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>B3-C3-P2</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>B3-C3-P2-S1,B3-C3-P2-S2,B3-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>19</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>B3-C2-P2</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>B3-C2-PART2[B3-C2-P2..B3-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>36</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>B3-C2-P2</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>B3-C2-P2-S1,B3-C2-P2-S2,B3-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>19</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>B3-C1-P2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>B3-C1-PART2[B3-C1-P2..B3-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>36</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>B3-C1-P2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>B3-C1-P2-S1,B3-C1-P2-S2,B3-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>inf_or_mech</t>
         </is>
@@ -18344,7 +20889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24446,6 +26991,642 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>19</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>B2-C3-PART1[B2-C3-P1..B2-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>72</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>B2-C3-P1,B2-C3-P3</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>B2-C3-P1-S1,B2-C3-P1-S2,B2-C3-P1-S3,B2-C3-P3-S1,B2-C3-P3-S2,B2-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>19</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>B2-C2-PART1[B2-C2-P1..B2-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>72</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>B2-C2-P1,B2-C2-P3</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>B2-C2-P1-S1,B2-C2-P1-S2,B2-C2-P1-S3,B2-C2-P3-S1,B2-C2-P3-S2,B2-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>19</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>B2-C1-PART1[B2-C1-P1..B2-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>72</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>B2-C1-P1,B2-C1-P3</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>B2-C1-P1-S1,B2-C1-P1-S2,B2-C1-P1-S3,B2-C1-P3-S1,B2-C1-P3-S2,B2-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>19</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>B2-C3-P2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>B2-C3-PART2[B2-C3-P2..B2-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>36</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>B2-C3</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>B2-C3-P2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>B2-C3-P2-S1,B2-C3-P2-S2,B2-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>19</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>B2-C2-P2</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>B2-C2-PART2[B2-C2-P2..B2-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>36</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>B2-C2</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>B2-C2-P2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>B2-C2-P2-S1,B2-C2-P2-S2,B2-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>19</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>B2-C1-P2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>B2-C1-PART2[B2-C1-P2..B2-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>36</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>B2-C1</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>B2-C1-P2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>B2-C1-P2-S1,B2-C1-P2-S2,B2-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>19</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>B3-C3-PART1[B3-C3-P1..B3-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>72</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>B3-C3-P1,B3-C3-P3</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>B3-C3-P1-S1,B3-C3-P1-S2,B3-C3-P1-S3,B3-C3-P3-S1,B3-C3-P3-S2,B3-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>19</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>B3-C2-PART1[B3-C2-P1..B3-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>72</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>B3-C2-P1,B3-C2-P3</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>B3-C2-P1-S1,B3-C2-P1-S2,B3-C2-P1-S3,B3-C2-P3-S1,B3-C2-P3-S2,B3-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>19</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>B3-C1-PART1[B3-C1-P1..B3-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>72</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>B3-C1-P1,B3-C1-P3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>B3-C1-P1-S1,B3-C1-P1-S2,B3-C1-P1-S3,B3-C1-P3-S1,B3-C1-P3-S2,B3-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>19</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>B3-C3-P2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>B3-C3-PART2[B3-C3-P2..B3-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>36</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>B3-C3-P2</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>B3-C3-P2-S1,B3-C3-P2-S2,B3-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>19</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>B3-C2-P2</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>B3-C2-PART2[B3-C2-P2..B3-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>36</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>B3-C2-P2</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>B3-C2-P2-S1,B3-C2-P2-S2,B3-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>19</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>B3-C1-P2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>B3-C1-PART2[B3-C1-P2..B3-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>36</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>B3-C1-P2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>B3-C1-P2-S1,B3-C1-P2-S2,B3-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,15 +478,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>blue_cas_inf_ground</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>blue_cas_inf_arty</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>blue_cas_armor_total</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>red_cas_inf_total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>red_cas_inf_ground</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>red_cas_inf_arty</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>red_cas_armor_total</t>
         </is>
@@ -512,10 +532,14 @@
         <v>11</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
         <v>19</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -544,13 +568,17 @@
       <c r="H3" t="n">
         <v>41</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>64</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -574,10 +602,14 @@
         <v>21</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -606,13 +638,17 @@
       <c r="H5" t="n">
         <v>46</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>14</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -643,13 +679,17 @@
       <c r="H6" t="n">
         <v>40</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -680,13 +720,17 @@
       <c r="H7" t="n">
         <v>79</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>44</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -717,13 +761,17 @@
       <c r="H8" t="n">
         <v>75</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>20</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -754,13 +802,17 @@
       <c r="H9" t="n">
         <v>24</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>27</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -791,13 +843,17 @@
       <c r="H10" t="n">
         <v>29</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>66</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -828,13 +884,17 @@
       <c r="H11" t="n">
         <v>120</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>33</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,13 +925,17 @@
       <c r="H12" t="n">
         <v>33</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>26</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,13 +966,17 @@
       <c r="H13" t="n">
         <v>21</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>7</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -939,13 +1007,17 @@
       <c r="H14" t="n">
         <v>19</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>30</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -976,13 +1048,17 @@
       <c r="H15" t="n">
         <v>25</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>23</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1013,13 +1089,17 @@
       <c r="H16" t="n">
         <v>29</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>11</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1050,13 +1130,17 @@
       <c r="H17" t="n">
         <v>50</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>47</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1087,13 +1171,17 @@
       <c r="H18" t="n">
         <v>12</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1124,13 +1212,17 @@
       <c r="H19" t="n">
         <v>17</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1161,13 +1253,17 @@
       <c r="H20" t="n">
         <v>124</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>12</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1198,13 +1294,17 @@
       <c r="H21" t="n">
         <v>77</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>56</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1235,13 +1335,17 @@
       <c r="H22" t="n">
         <v>43</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>16</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1272,13 +1376,17 @@
       <c r="H23" t="n">
         <v>73</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>12</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1309,13 +1417,107 @@
       <c r="H24" t="n">
         <v>53</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>12</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>18</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>47</v>
+      </c>
+      <c r="I26" t="n">
+        <v>47</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>101</v>
+      </c>
+      <c r="M26" t="n">
+        <v>37</v>
+      </c>
+      <c r="N26" t="n">
+        <v>64</v>
+      </c>
+      <c r="O26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1330,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q190"/>
+  <dimension ref="A1:Q222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14126,6 +14328,2054 @@
       <c r="Q190" t="inlineStr">
         <is>
           <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>19</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="n">
+        <v>31</v>
+      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>19</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="n">
+        <v>7</v>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>19</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="n">
+        <v>62</v>
+      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>19</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="n">
+        <v>3</v>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>19</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>72</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>3</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>10</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>5</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>19</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>36</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>5</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>2</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>19</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>35</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>3</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>19</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>69</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>36</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>19</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>69</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>3</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>19</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>36</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>36</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>19</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>34</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>3</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>19</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>72</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>2</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>19</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>72</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>72</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>19</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>34</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>72</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>19</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>34</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>36</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>1</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>19</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>31</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>29</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>19</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:15:00</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>72</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>28</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>4</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>19</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:15:00</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>29</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>70</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>19</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:30:00</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>28</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>19</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="n">
+        <v>13</v>
+      </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>19</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="n">
+        <v>16</v>
+      </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>19</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="n">
+        <v>31</v>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>19</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>19</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>72</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>4</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>19</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>36</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>19</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>68</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>36</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>19</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>36</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>5</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>72</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>19</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>67</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>2</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>56</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>17</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>19</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>31</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>25</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>59</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>19</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>72</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>4</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>39</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>19</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>19</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>65</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>2</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>72</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>19</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>36</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>4</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>разгром</t>
         </is>
       </c>
     </row>
@@ -14140,7 +16390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20873,6 +23123,642 @@
         </is>
       </c>
       <c r="K127" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>19</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>72</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>19</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>72</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>19</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>72</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>19</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>36</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>19</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>36</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>19</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>36</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>19</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>72</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>19</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>72</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>19</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>72</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>19</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>36</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>19</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>36</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>19</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>36</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>inf_or_mech</t>
         </is>
@@ -20889,7 +23775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27627,6 +30513,642 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>19</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>72</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>19</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>72</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>19</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>72</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>19</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>36</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>19</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>36</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>19</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>36</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>19</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>72</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>19</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>72</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>19</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>72</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>19</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>36</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>19</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>36</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>19</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>36</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,6 +1518,104 @@
         <v>64</v>
       </c>
       <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>65</v>
+      </c>
+      <c r="I27" t="n">
+        <v>65</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>92</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46155.41666666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B10 на север в горы</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>200</v>
+      </c>
+      <c r="M28" t="n">
+        <v>34</v>
+      </c>
+      <c r="N28" t="n">
+        <v>166</v>
+      </c>
+      <c r="O28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1532,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q222"/>
+  <dimension ref="A1:Q255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16376,6 +16474,2103 @@
       <c r="Q222" t="inlineStr">
         <is>
           <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>19</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="n">
+        <v>32</v>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>19</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>19</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="n">
+        <v>22</v>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>19</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="n">
+        <v>20</v>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>19</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>72</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>52</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>19</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>72</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>16</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>72</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>19</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>36</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>14</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
+        <v>5</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>19</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>72</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>3</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>19</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>36</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>23</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>72</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>19</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>70</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>9</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>3</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>19</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>68</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>36</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>19</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>13</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>13</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>72</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>19</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>35</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>3</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>6</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>2</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>19</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>72</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>4</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>19</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>67</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>3</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>2</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>19</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>36</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>36</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>3</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>19</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="n">
+        <v>72</v>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>19</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="n">
+        <v>28</v>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>19</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="n">
+        <v>36</v>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>19</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="n">
+        <v>25</v>
+      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>19</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="n">
+        <v>5</v>
+      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>19</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>72</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>72</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>14</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>19</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>36</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>11</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="n">
+        <v>11</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>19</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>35</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>3</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="n">
+        <v>2</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>19</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>72</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>4</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>разгром</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>19</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:00:00</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>72</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>72</v>
+      </c>
+      <c r="M248" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>19</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:15:00</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>36</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>5</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>72</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>19</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>68</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>3</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>58</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="n">
+        <v>3</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>19</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>69</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>4</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>72</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>19</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>31</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>55</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0</v>
+      </c>
+      <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>победа</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>19</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:45:00</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>36</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
+        <v>5</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>72</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>поражение</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>19</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:15:00</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>31</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>8</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>53</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>засада</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>19</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:30:00</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>69</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>52</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>inf_attacks_inf</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>ничья</t>
         </is>
       </c>
     </row>
@@ -16390,7 +18585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23759,6 +25954,642 @@
         </is>
       </c>
       <c r="K139" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>19</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>72</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>19</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>72</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>19</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>72</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>19</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>36</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>19</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>36</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>19</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>36</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>19</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>72</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>19</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>72</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>19</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>72</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>19</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>36</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>19</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>36</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>19</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>36</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>inf_or_mech</t>
         </is>
@@ -23775,7 +26606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31149,6 +33980,642 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>19</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>72</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>19</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>72</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>19</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>72</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>19</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>36</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>19</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>36</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>19</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>36</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>19</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>72</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>19</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>72</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>19</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>72</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>19</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>36</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>19</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>36</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>19</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>36</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tactical_battle_log.xlsx
+++ b/tactical_battle_log.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tactical_log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ground_log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46155.41666666666</v>
+        <v>46155.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,22 +525,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -547,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="M2" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -561,27 +563,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>46155.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B1 против B1</t>
+          <t>B2 против B2</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>56</v>
@@ -596,67 +598,16 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="M3" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
         <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:00:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>B2 рубиццо</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>32</v>
-      </c>
-      <c r="I4" t="n">
-        <v>32</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -670,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +717,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-13 10:00:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -774,59 +725,39 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BLU_2</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mlrs</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>RED_5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>36</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>18</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>разгром</t>
-        </is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -835,7 +766,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-13 10:15:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -843,59 +774,39 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BLU_2</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mlrs</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>RED_6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>36</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>победа</t>
-        </is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -904,7 +815,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13 10:15:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -912,59 +823,39 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mlrs</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>RED_5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>18</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>победа</t>
-        </is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -973,7 +864,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-13 10:30:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,59 +872,39 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mlrs</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>RED_6</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>27</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>5</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>засада</t>
-        </is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1042,7 +913,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-13 10:45:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1052,7 +923,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BLU_3</t>
+          <t>BLU_6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1061,20 +932,20 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>RED_6</t>
+          <t>RED_4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1083,13 +954,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1101,7 +972,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>засада</t>
         </is>
       </c>
     </row>
@@ -1111,7 +982,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-13 11:00:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1121,7 +992,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BLU_4</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1130,7 +1001,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1143,7 +1014,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>RED_6</t>
+          <t>RED_2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1152,13 +1023,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1180,7 +1051,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-13 10:30:00</t>
+          <t>2026-05-13 12:15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1190,7 +1061,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BLU_2</t>
+          <t>BLU_6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1199,20 +1070,20 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RED_5</t>
+          <t>RED_1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1221,13 +1092,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1239,7 +1110,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>засада</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1120,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-13 10:00:00</t>
+          <t>2026-05-13 12:30:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1259,7 +1130,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1268,7 +1139,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1281,7 +1152,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1290,13 +1161,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1308,7 +1179,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>победа</t>
+          <t>разгром</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1189,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-13 11:15:00</t>
+          <t>2026-05-13 12:15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1328,7 +1199,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BLU_4</t>
+          <t>BLU_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1337,20 +1208,20 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1359,13 +1230,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1387,7 +1258,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-13 11:30:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1395,59 +1266,41 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>BLU_4</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>cannon</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>RED_4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>32</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>победа</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -1456,7 +1309,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-13 11:15:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1464,59 +1317,41 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BLU_5</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>cannon</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>RED_6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
+        <v>16</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>победа</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -1525,7 +1360,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-13 11:00:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1533,59 +1368,41 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>cannon</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>RED_1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>72</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>ничья</t>
-        </is>
+          <t>art_air_fire</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1594,7 +1411,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-13 11:45:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1604,7 +1421,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BLU_4</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1613,47 +1430,47 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>RED_4</t>
+          <t>RED_2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ничья</t>
+          <t>поражение</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1480,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-13 10:45:00</t>
+          <t>2026-05-13 12:15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1673,7 +1490,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BLU_2</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1682,13 +1499,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1700,14 +1517,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1717,12 +1534,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>ничья</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1549,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-13 11:30:00</t>
+          <t>2026-05-13 12:00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1742,7 +1559,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1751,13 +1568,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1773,13 +1590,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1791,86 +1608,86 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>победа</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>31</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-13 12:00:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BLU_4</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>36</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>RED_4</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>36</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ничья</t>
+          <t>победа</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-13 12:00:00</t>
+          <t>2026-05-13 12:15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1880,7 +1697,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BLU_1</t>
+          <t>BLU_6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1889,20 +1706,20 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>RED_1</t>
+          <t>RED_3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1911,13 +1728,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1929,17 +1746,17 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>засада</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-13 12:00:00</t>
+          <t>2026-05-13 12:30:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1949,7 +1766,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BLU_2</t>
+          <t>BLU_5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1958,7 +1775,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1971,44 +1788,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>RED_3</t>
+          <t>RED_7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_armor</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>разгром</t>
+          <t>anti_armor_attack</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-13 12:15:00</t>
+          <t>2026-05-13 12:45:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2018,7 +1835,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BLU_4</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2027,57 +1844,57 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RED_5</t>
+          <t>RED_7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_armor</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>поражение</t>
+          <t>anti_armor_attack</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-13 12:30:00</t>
+          <t>2026-05-13 13:00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2087,7 +1904,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BLU_3</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2096,101 +1913,101 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>RED_5</t>
+          <t>RED_4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>разгром</t>
+          <t>засада</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:15:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-13 12:45:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BLU_3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>59</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28</v>
-      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>RED_6</t>
+          <t>RED_4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2200,22 +2017,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>засада</t>
+          <t>поражение</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-13 12:15:00</t>
+          <t>2026-05-13 13:30:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2225,7 +2042,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BLU_5</t>
+          <t>BLU_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2234,57 +2051,57 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>RED_1</t>
+          <t>RED_4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ничья</t>
+          <t>разгром</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-13 12:15:00</t>
+          <t>2026-05-13 13:15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2294,7 +2111,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BLU_6</t>
+          <t>BLU_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2303,254 +2120,1671 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>84</v>
+      </c>
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>RED_4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>34</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>inf_attacks_inf</t>
+          <t>inf_attacks_mech</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ничья</t>
+          <t>поражение</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:15:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>83</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>mech</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>26</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>inf_attacks_mech</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ничья</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tactical_buttle_num</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>temp_unit_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source_uid</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slice_label</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>split_basis</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>soldiers</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>company_uids</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>platoon_uids</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>squad_uids</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>84</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BLU_1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>84</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BLU_2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>84</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BLU_3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>B1-C1-P2,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BLU_4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>42</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BLU_5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>42</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BLU_6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>B1-C1-P1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P1]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>37</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>B1-C1-P1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tactical_buttle_num</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>temp_unit_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source_uid</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slice_label</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>split_basis</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>soldiers</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>company_uids</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>platoon_uids</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>squad_uids</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>unit_role_armor</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>assigned_armor</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>source_armor_uids</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B1-C3-PART1[B1-C3-P1..B1-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>84</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>B1-C3-P1,B1-C3-P3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>B1-C3-P1-S1,B1-C3-P1-S2,B1-C3-P1-S3,B1-C3-P3-S1,B1-C3-P3-S2,B1-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B1-C2-PART1[B1-C2-P1..B1-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>B1-C2-P1,B1-C2-P3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B1-C2-P1-S1,B1-C2-P1-S2,B1-C2-P1-S3,B1-C2-P3-S1,B1-C2-P3-S2,B1-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B1-C1-PART1[B1-C1-P1..B1-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>B1-C1-P1,B1-C1-P3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>B1-C1-P1-S1,B1-C1-P1-S2,B1-C1-P1-S3,B1-C1-P3-S1,B1-C1-P3-S2,B1-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B1-C3-PART2[B1-C3-P2..B1-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>B1-C3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>B1-C3-P2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>B1-C3-P2-S1,B1-C3-P2-S2,B1-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B1-C2-PART2[B1-C2-P2..B1-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>B1-C2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>B1-C2-P2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>B1-C2-P2-S1,B1-C2-P2-S2,B1-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B1-C1-PART2[B1-C1-P2..B1-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>B1-C1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>B1-C1-P2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B1-C1-P2-S1,B1-C1-P2-S2,B1-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RED_1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>B3-C3-PART1[B3-C3-P1..B3-C3-P3]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>84</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>B3-C3-P1,B3-C3-P3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B3-C3-P1-S1,B3-C3-P1-S2,B3-C3-P1-S3,B3-C3-P3-S1,B3-C3-P3-S2,B3-C3-P3-S3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RED_2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>B3-C2-PART1[B3-C2-P1..B3-C2-P3]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>84</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>B3-C2-P1,B3-C2-P3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>B3-C2-P1-S1,B3-C2-P1-S2,B3-C2-P1-S3,B3-C2-P3-S1,B3-C2-P3-S2,B3-C2-P3-S3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:00:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>pc1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>108</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>b2_c2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>разгром</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>A28,A29,A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RED_3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>B3-C1-PART1[B3-C1-P1..B3-C1-P3]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>84</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>B3-C1-P1,B3-C1-P3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B3-C1-P1-S1,B3-C1-P1-S2,B3-C1-P1-S3,B3-C1-P3-S1,B3-C1-P3-S2,B3-C1-P3-S3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RED_4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B3-C3-P2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>B3-C3-PART2[B3-C3-P2..B3-C3-P2]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>42</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B3-C3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>B3-C3-P2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B3-C3-P2-S1,B3-C3-P2-S2,B3-C3-P2-S3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:00:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>pc1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>108</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>b2_c2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>засада</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:00:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>pc1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>108</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>32</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>b2_c2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>107</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>засада</t>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>A30,A5,A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RED_5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B3-C2-P2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>B3-C2-PART2[B3-C2-P2..B3-C2-P2]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>42</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B3-C2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>B3-C2-P2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>B3-C2-P2-S1,B3-C2-P2-S2,B3-C2-P2-S3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>A4,A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RED_6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>B3-C1-P2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>B3-C1-PART2[B3-C1-P2..B3-C1-P2]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>platoon</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>42</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>B3-C1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>B3-C1-P2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>B3-C1-P2-S1,B3-C1-P2-S2,B3-C1-P2-S3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>inf_or_mech</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>mech_attachment</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>A3,A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RED_7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RED_7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>20</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>A1,A10,A11,A12,A13,A14,A15,A16,A17,A18,A19,A2,A20,A21,A22,A23,A24,A25,A26,A27</t>
         </is>
       </c>
     </row>
